--- a/sample-data/test-scenarios/test-2-missing-dl/Pacific_Freight_Lines_Vehicle_Schedule.xlsx
+++ b/sample-data/test-scenarios/test-2-missing-dl/Pacific_Freight_Lines_Vehicle_Schedule.xlsx
@@ -489,12 +489,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>80,000 lbs</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$85,000</t>
+          <t>$95,000</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>80,000 lbs</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$85,000</t>
+          <t>$95,000</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>80,000 lbs</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$85,000</t>
+          <t>$95,000</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>80,000 lbs</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$85,000</t>
+          <t>$95,000</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>80,000 lbs</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$85,000</t>
+          <t>$95,000</t>
         </is>
       </c>
     </row>
